--- a/quizzes/007_external_links_access_quiz--quizzes.xlsx
+++ b/quizzes/007_external_links_access_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'safe_link'}</t>
+          <t>safe_link</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'safe_link'}</t>
+          <t>safe link</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'unsafe_link'}</t>
+          <t>unsafe_link</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'unsafe_link'}</t>
+          <t>unsafe link</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'category_a'}</t>
+          <t>category_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'category_a'}</t>
+          <t>category a</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'category_b'}</t>
+          <t>category_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'category_b'}</t>
+          <t>category b</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'category_c'}</t>
+          <t>category_c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'category_c'}</t>
+          <t>category c</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'internal_source'}</t>
+          <t>internal_source</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 'internal_source'}</t>
+          <t>internal source</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'external_source'}</t>
+          <t>external_source</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'external_source'}</t>
+          <t>external source</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'direct_link'}</t>
+          <t>direct_link</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'direct_link'}</t>
+          <t>direct link</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'embedded_link'}</t>
+          <t>embedded_link</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'embedded_link'}</t>
+          <t>embedded link</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': 'option_1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': 'option_2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 'option_3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
